--- a/EnergyPrices and Supporting Data/2014Prices/Energy Rates_2014.xlsx
+++ b/EnergyPrices and Supporting Data/2014Prices/Energy Rates_2014.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="57510" yWindow="-90" windowWidth="23235" windowHeight="12555"/>
+    <workbookView xWindow="57510" yWindow="-90" windowWidth="23235" windowHeight="12555" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="5" r:id="rId1"/>
@@ -1309,7 +1309,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1615,7 +1614,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2439,7 +2437,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="1600" b="1"/>
-              <a:t>Prize (August</a:t>
+              <a:t>Price (August</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" sz="1600" b="1" baseline="0"/>
@@ -2449,6 +2447,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2748,6 +2747,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2978,6 +2978,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3299,6 +3300,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3417,6 +3419,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4666,7 +4669,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4976,7 +4978,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>

--- a/EnergyPrices and Supporting Data/2014Prices/Energy Rates_2014.xlsx
+++ b/EnergyPrices and Supporting Data/2014Prices/Energy Rates_2014.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="57510" yWindow="-90" windowWidth="23235" windowHeight="12555" activeTab="4"/>
+    <workbookView xWindow="57510" yWindow="-90" windowWidth="23235" windowHeight="12555" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="5" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="September" sheetId="10" r:id="rId8"/>
     <sheet name="March" sheetId="7" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1309,6 +1309,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1614,6 +1615,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2978,7 +2980,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3300,7 +3301,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3419,7 +3419,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3587,7 +3586,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3897,7 +3895,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4128,7 +4125,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4438,7 +4434,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
